--- a/tv_trading_journal.xlsx
+++ b/tv_trading_journal.xlsx
@@ -10,6 +10,7 @@
     <sheet name="All_Trades" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Nifty_Option_Scalp" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Silvermic_15M" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Unknown_Scalp_Strategy" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,16 +440,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -457,8 +458,8 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="17" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="72" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="146" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -719,6 +720,93 @@
       <c r="Q3" t="inlineStr">
         <is>
           <t>Successfully placed via TradingView webhook (Rule: rule_silvermic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TV_UNMATCHED_Unknown__20260909214956</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>21:49:56</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>test_alert_9999</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Unknown_Scalp_Strategy</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>UNMATCHED</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CRUDEOIL26OCTFUT</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CRUDEOIL26OCTFUT</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>6520.00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>NO_ORDER</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NO_MATCHING_STRATEGY</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>⚠️ Alert received for strategy 'Unknown_Scalp_Strategy' (BUY CRUDEOIL26OCTFUT) but no active strategy rule is configured in tv_strategies.json</t>
         </is>
       </c>
     </row>
@@ -1139,4 +1227,211 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="146" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Trade_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Alert_ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Strategy_Name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Execution_Mode</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Underlying</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Tradingsymbol</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Exchange</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Order_Type</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Trigger_LTP</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Kite_Order_ID</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Execution_Status</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TV_UNMATCHED_Unknown__20260909214956</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>21:49:56</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>test_alert_9999</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Unknown_Scalp_Strategy</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>UNMATCHED</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CRUDEOIL26OCTFUT</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CRUDEOIL26OCTFUT</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>6520.00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>NO_ORDER</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>NO_MATCHING_STRATEGY</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>⚠️ Alert received for strategy 'Unknown_Scalp_Strategy' (BUY CRUDEOIL26OCTFUT) but no active strategy rule is configured in tv_strategies.json</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>